--- a/resource/groundTruths/CF_M01_ground_truth.xlsx
+++ b/resource/groundTruths/CF_M01_ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2D3EAD-43B2-BE48-8762-AF148F234680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B25612F-AF60-4740-985A-DA7429B05E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="1240" windowWidth="27900" windowHeight="16380" xr2:uid="{B9042A1C-F04E-764E-995C-620B219A95D4}"/>
   </bookViews>
@@ -40,9 +40,6 @@
     <t>CF_M01_R01</t>
   </si>
   <si>
-    <t>That the system saves the players' playlogs</t>
-  </si>
-  <si>
     <t>FR</t>
   </si>
   <si>
@@ -58,9 +55,6 @@
     <t>CF_M01_R03</t>
   </si>
   <si>
-    <t>Let the system save player connections</t>
-  </si>
-  <si>
     <t>CF_M01_R04</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t>CF_M01_R06</t>
   </si>
   <si>
-    <t>That the system saves the actions carried out on the platform</t>
-  </si>
-  <si>
     <t>CF_M01_R07</t>
   </si>
   <si>
@@ -116,9 +107,6 @@
   </si>
   <si>
     <t>CF_M01_R13</t>
-  </si>
-  <si>
-    <t>The connections that the user will be able to see will depend on the permissions you have.</t>
   </si>
   <si>
     <t>CF_M01_R14</t>
@@ -137,9 +125,6 @@
     <t>CF_M01_R16</t>
   </si>
   <si>
-    <t>The actions that the user will be able to see will depend on the permissions what does it have</t>
-  </si>
-  <si>
     <t>CF_M01_R015</t>
   </si>
   <si>
@@ -304,6 +289,21 @@
   </si>
   <si>
     <t>Applied Fixes</t>
+  </si>
+  <si>
+    <t>System saves the players' playlogs</t>
+  </si>
+  <si>
+    <t>System saves player connections</t>
+  </si>
+  <si>
+    <t>System saves the actions carried out on the platform</t>
+  </si>
+  <si>
+    <t>The connections that the user will be able to see will depend on the permissions it has.</t>
+  </si>
+  <si>
+    <t>The actions that the user will be able to see will depend on the permissions it has</t>
   </si>
 </sst>
 </file>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -572,6 +572,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -892,45 +898,45 @@
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="G1" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="H1" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="I1" s="27" t="s">
         <v>82</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="27" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -942,16 +948,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -965,16 +971,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -986,21 +992,21 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" s="5">
         <v>35</v>
@@ -1009,21 +1015,21 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="11">
         <v>35</v>
@@ -1032,16 +1038,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -1053,21 +1059,21 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2">
         <v>36</v>
@@ -1076,21 +1082,21 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H9" s="15">
         <v>36</v>
@@ -1099,16 +1105,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -1120,21 +1126,21 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H11" s="5">
         <v>36</v>
@@ -1143,21 +1149,21 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2">
         <v>36</v>
@@ -1166,16 +1172,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -1187,21 +1193,21 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2">
         <v>36</v>
@@ -1210,39 +1216,39 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
       <c r="G15" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H15" s="15">
         <v>36</v>
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="126" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>27</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -1254,21 +1260,21 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H17" s="5">
         <v>37</v>
@@ -1277,21 +1283,21 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H18" s="2">
         <v>37</v>
@@ -1300,22 +1306,22 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
@@ -1325,21 +1331,21 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H20" s="11">
         <v>37</v>
@@ -1348,22 +1354,22 @@
     </row>
     <row r="21" spans="1:9" ht="104" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="20">
@@ -1373,45 +1379,45 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="9"/>
       <c r="G22" s="16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H22" s="20">
         <v>38</v>
       </c>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="126" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>47</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
@@ -1421,22 +1427,22 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G24" s="18"/>
       <c r="H24" s="11">
@@ -1444,24 +1450,24 @@
       </c>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="168" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>53</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
@@ -1471,21 +1477,21 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H26" s="11">
         <v>39</v>
@@ -1494,22 +1500,22 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
@@ -1519,21 +1525,21 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H28" s="2">
         <v>39</v>
@@ -1542,16 +1548,16 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E29" s="23"/>
       <c r="F29" s="23"/>
@@ -1563,16 +1569,16 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
@@ -1584,16 +1590,16 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
@@ -1605,16 +1611,16 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>

--- a/resource/groundTruths/CF_M01_ground_truth.xlsx
+++ b/resource/groundTruths/CF_M01_ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B25612F-AF60-4740-985A-DA7429B05E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35013314-6C8E-0E4D-A39F-A256C173D0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="1240" windowWidth="27900" windowHeight="16380" xr2:uid="{B9042A1C-F04E-764E-995C-620B219A95D4}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="85">
   <si>
     <t>CF_M01_R01</t>
   </si>
@@ -170,13 +170,6 @@
     <t>CF_M01_R21</t>
   </si>
   <si>
-    <t>Any user must be able to access the platform during any time
-time of day. Except for scheduled updates.</t>
-  </si>
-  <si>
-    <t>CF_M01_R020</t>
-  </si>
-  <si>
     <t>CF_M01_R22</t>
   </si>
   <si>
@@ -199,10 +192,6 @@
     <t>CF_M01_R24</t>
   </si>
   <si>
-    <t>The project's functionalities must only be accessible to
-users with the corresponding permissions.</t>
-  </si>
-  <si>
     <t>15a. Access</t>
   </si>
   <si>
@@ -210,12 +199,6 @@
   </si>
   <si>
     <t>Unauthorized users cannot access data they do not own.</t>
-  </si>
-  <si>
-    <t>CF_M01_R024</t>
-  </si>
-  <si>
-    <t>CF_M01_R26</t>
   </si>
   <si>
     <t>Users' confidential information must be protected in order to
@@ -231,9 +214,6 @@
     <t>Users can only view their confidential data user and no one else.</t>
   </si>
   <si>
-    <t>CF_M01_R026</t>
-  </si>
-  <si>
     <t>CF_M01_R28</t>
   </si>
   <si>
@@ -304,6 +284,15 @@
   </si>
   <si>
     <t>The actions that the user will be able to see will depend on the permissions it has</t>
+  </si>
+  <si>
+    <t>The project's functionalities must only be accessible to users with the corresponding permissions.</t>
+  </si>
+  <si>
+    <t>CF_M01_R023</t>
+  </si>
+  <si>
+    <t>CF_M01_R025</t>
   </si>
 </sst>
 </file>
@@ -893,47 +882,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C82703-F87B-504A-AB2C-06A09EABBD61}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="H1" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="I1" s="27" t="s">
         <v>76</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="27" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>1</v>
@@ -948,7 +937,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>2</v>
@@ -971,13 +960,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -992,7 +981,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
@@ -1015,7 +1004,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>8</v>
@@ -1038,13 +1027,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>1</v>
@@ -1059,7 +1048,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>11</v>
@@ -1082,7 +1071,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>13</v>
@@ -1105,7 +1094,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>15</v>
@@ -1126,7 +1115,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>17</v>
@@ -1149,7 +1138,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>19</v>
@@ -1172,7 +1161,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>21</v>
@@ -1193,13 +1182,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>4</v>
@@ -1216,7 +1205,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>24</v>
@@ -1239,7 +1228,7 @@
     </row>
     <row r="16" spans="1:9" ht="126" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>26</v>
@@ -1260,13 +1249,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>4</v>
@@ -1283,7 +1272,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>30</v>
@@ -1306,7 +1295,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>32</v>
@@ -1331,7 +1320,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>37</v>
@@ -1354,7 +1343,7 @@
     </row>
     <row r="21" spans="1:9" ht="104" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>40</v>
@@ -1377,258 +1366,235 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="16" t="s">
+    <row r="22" spans="1:9" ht="126" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5">
+        <v>38</v>
+      </c>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="20">
-        <v>38</v>
-      </c>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:9" ht="126" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="C23" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>48</v>
+      <c r="E23" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5">
+      <c r="G23" s="18"/>
+      <c r="H23" s="11">
         <v>38</v>
       </c>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
-        <v>73</v>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9" ht="154" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="11">
-        <v>38</v>
-      </c>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9" ht="168" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>73</v>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5">
+        <v>39</v>
+      </c>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="11">
+        <v>39</v>
+      </c>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" ht="112" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="C26" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="9" t="s">
+      <c r="E26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5">
+      <c r="G26" s="5"/>
+      <c r="H26" s="5">
         <v>39</v>
       </c>
-      <c r="I25" s="6"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="C27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H26" s="11">
+      <c r="E27" s="2"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="2">
         <v>39</v>
       </c>
-      <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="9" t="s">
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C28" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="D28" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5">
-        <v>39</v>
-      </c>
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23">
+        <v>40</v>
+      </c>
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9" t="s">
+      <c r="D29" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25">
+        <v>40</v>
+      </c>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="H28" s="2">
-        <v>39</v>
-      </c>
-      <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="22" t="s">
+      <c r="C30" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="D30" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23">
+        <v>40</v>
+      </c>
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="C31" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23">
+      <c r="D31" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25">
         <v>40</v>
       </c>
-      <c r="I29" s="6"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25">
-        <v>40</v>
-      </c>
-      <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23">
-        <v>40</v>
-      </c>
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25">
-        <v>40</v>
-      </c>
-      <c r="I32" s="3"/>
+      <c r="I31" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/groundTruths/CF_M01_ground_truth.xlsx
+++ b/resource/groundTruths/CF_M01_ground_truth.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35013314-6C8E-0E4D-A39F-A256C173D0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B5CB89-60C4-BE49-A6FA-778526E9EE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="1240" windowWidth="27900" windowHeight="16380" xr2:uid="{B9042A1C-F04E-764E-995C-620B219A95D4}"/>
   </bookViews>
